--- a/Data/EXCEL/Transfer/salemon/202602/9933-salemon-202602.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202602/9933-salemon-202602.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C8B3AF7-CCD8-46E7-8E72-3D35EF4BA4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33C3EF08-2C89-4407-87D5-F8F17613333A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{2A89E9AD-9894-458F-801D-F5CC9578579F}"/>
+    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{DD075BED-D7B9-4F3E-B6F0-096257A9E43F}"/>
   </bookViews>
   <sheets>
     <sheet name="9933-salemon-202602" sheetId="2" r:id="rId1"/>
@@ -1264,7 +1264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12570EB-16F6-40AD-906A-AE2455CE82E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F3C827-A5C6-42CB-B119-D0D551198550}">
   <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
